--- a/Assets/06.Data/Origin/EnemyData.xlsx
+++ b/Assets/06.Data/Origin/EnemyData.xlsx
@@ -473,6 +473,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:K14"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
@@ -587,7 +596,7 @@
         <v>13</v>
       </c>
       <c r="F4">
-        <v>5</v>
+        <v>2000</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -928,5 +937,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>